--- a/zy70725/reports/scan_result_6bb0fca69e68.xlsx
+++ b/zy70725/reports/scan_result_6bb0fca69e68.xlsx
@@ -632,12 +632,24 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>无空值，可直接恢复严格校验</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-19T13:14:18.850189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -673,12 +685,24 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>仍有1.5%空值，需要延长例外期</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-05-19T13:15:14.577977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
